--- a/assessment/templates/privacy-officer-checklist.xlsx
+++ b/assessment/templates/privacy-officer-checklist.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Privacy impact assessment for Copilot NPI processing; DLP policy configuration preventing NPI surfacing outside authorized workflows; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
+          <t>Privacy impact assessment for Copilot NPI processing; Custom DLP policy configuration showing the Copilot location, applicable supported actions, mode, scope, and alerts; Synthetic tests for label exclusion, typed-prompt blocking where available, web-search restriction, external-email exclusion where available, and the direct-upload limitation; Purview Audit CopilotInteraction evidence and DSPM AI activity review; Copilot Pages and Notebooks SharePoint Embedded limitation review and admin-policy disposition; SEC Reg S-P alignment documentation for Copilot; GLBA §501(b) safeguards review covering Copilot</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
